--- a/data/externalStats/File1/RPT_RPT5721799034895YM_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT5721799034895YM_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>28321869.63325635</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>37842.22928475847</v>
+        <v>37842.22928475848</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2412,7 +2412,7 @@
         <v>7349724.884596495</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>563.805105</v>
+        <v>563.8051049999999</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>5564.442124999999</v>
+        <v>5564.442124999998</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>6188704.374589606</v>
+        <v>6188704.374589607</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>3352.283312</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>3570747.059741252</v>
+        <v>3570747.059741253</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>12396.8159518388</v>
@@ -2777,7 +2777,7 @@
         <v>2901313.69343935</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>354.0840958925122</v>
+        <v>354.0840958925123</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -3085,7 +3085,7 @@
         <v>1886765.755512451</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>432.3470500000001</v>
+        <v>432.34705</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -3292,7 +3292,7 @@
         <v>1571920.225377287</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>3118.807607</v>
+        <v>3118.807606999999</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>49532560.64458299</v>
+        <v>49532560.644583</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>6991.811105496875</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>42381311.56098315</v>
+        <v>42381311.56098316</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>56332.87391490716</v>
@@ -3905,13 +3905,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18456847241</v>
+        <v>6320.184568472409</v>
       </c>
       <c r="K53" s="128" t="n">
         <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7692560352087</v>
+        <v>790.7692560352083</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>6124.982752775582</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254566</v>
+        <v>3021.852223254567</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8856898136659</v>
+        <v>757.8856898136662</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -3935,19 +3935,19 @@
         <v>9904.720665843814</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.678172337912</v>
+        <v>5957.678172337913</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.103304474578</v>
+        <v>2933.103304474579</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.1979185924263</v>
+        <v>729.1979185924259</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.979395404916</v>
+        <v>9619.979395404918</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -3989,7 +3989,7 @@
         <v>14502.01308940453</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860365</v>
+        <v>7845.496351860367</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.677045112664</v>
@@ -3998,22 +3998,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>24673.18648637756</v>
+        <v>24673.18648637757</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>15888.66465948535</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>8427.48817443864</v>
+        <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.15733677209</v>
+        <v>26997.1573367721</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.25159470503</v>
@@ -4042,7 +4042,7 @@
         <v>2540465.730080406</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>408.3996518600001</v>
+        <v>408.39965186</v>
       </c>
     </row>
     <row r="55">
@@ -4070,7 +4070,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>84.18113861466703</v>
@@ -4085,10 +4085,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -4100,10 +4100,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>2306976.04974127</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>669.4806582952169</v>
+        <v>669.480658295217</v>
       </c>
     </row>
     <row r="57">
@@ -4229,19 +4229,19 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.402957708949</v>
+        <v>6294.40295770895</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>437.3875171463492</v>
+        <v>437.387517146349</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262969340319</v>
+        <v>8174.262969340318</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.281402399409</v>
@@ -4250,7 +4250,7 @@
         <v>1116.162906236298</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>418.4625294433528</v>
+        <v>418.462529443353</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>258.2282688764468</v>
@@ -4259,19 +4259,19 @@
         <v>8033.135106955507</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6382.359151572182</v>
+        <v>6382.359151572181</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1131.374266204664</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.6902841248111</v>
+        <v>419.6902841248108</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8200.83017629315</v>
+        <v>8200.830176293148</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -4715,34 +4715,34 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.086825987135</v>
+        <v>5569.086825987128</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939058</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>647.3668914722069</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829597368207</v>
+        <v>8460.829597368198</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5846.165470626176</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486477</v>
+        <v>1696.460671486473</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667296</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>738.1509877393058</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514426118691</v>
+        <v>8909.514426118685</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6142.898890084994</v>
@@ -4852,7 +4852,7 @@
         <v>716582.3096759347</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>519.9018866372211</v>
+        <v>519.9018866372212</v>
       </c>
     </row>
     <row r="65">
@@ -5138,7 +5138,7 @@
         <v>899.5669733810392</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72510.53378779674</v>
+        <v>72510.53378779672</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>54059.89244389046</v>
@@ -5182,7 +5182,7 @@
         <v>334889.571394201</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>1877.738034182705</v>
+        <v>1877.738034182704</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -5336,13 +5336,13 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6288.269408740671</v>
+        <v>6288.269408740672</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1107.836161362766</v>
+        <v>1107.836161362765</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1518534315276</v>
+        <v>357.1518534315275</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -5351,13 +5351,13 @@
         <v>7753.257423534964</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6400.337036322164</v>
+        <v>6400.337036322165</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9303875207317</v>
+        <v>365.9303875207316</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
@@ -5366,7 +5366,7 @@
         <v>7907.087201444931</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.941393404507</v>
+        <v>6479.941393404506</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.179193274199</v>
+        <v>8024.179193274198</v>
       </c>
     </row>
     <row r="72">
@@ -5421,7 +5421,7 @@
         <v>3.034002090881227</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.9993468012388085</v>
+        <v>0.9993468012388083</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.033348892120036</v>
+        <v>4.033348892120035</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.003844360738305</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="132" t="n">
-        <v>3.992985467227335</v>
+        <v>3.992985467227334</v>
       </c>
     </row>
     <row r="73">
@@ -5555,7 +5555,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -5610,7 +5610,7 @@
         <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0635744741532</v>
+        <v>498.0635744741531</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -5628,19 +5628,19 @@
         <v>573.2360613407959</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138078</v>
+        <v>200.6429391138079</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73441812211</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.510987948814</v>
+        <v>9710.510987948812</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>633.2429903122046</v>
+        <v>633.2429903122047</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>215.8071055370164</v>
@@ -6009,46 +6009,46 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="L81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="132" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="P81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="131" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="R81" s="131" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="S81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="132" t="n">
+        <v>5.684341886080801e-13</v>
+      </c>
+      <c r="V81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="131" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="M81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="132" t="n">
-        <v>-2.501110429875553e-12</v>
-      </c>
-      <c r="P81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="Q81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="132" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="V81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="W81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
-      </c>
       <c r="Y81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>-3.751665644813329e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="82">
@@ -6357,7 +6357,7 @@
         <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>19086.22657346602</v>
+        <v>19086.22657346603</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>15525.14577929941</v>
@@ -6369,7 +6369,7 @@
         <v>939.1664488615277</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869956</v>
+        <v>210.6296420869957</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>20593.2471536308</v>
@@ -6387,7 +6387,7 @@
         <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>21876.19741018457</v>
+        <v>21876.19741018458</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6574,7 +6574,7 @@
         <v>12437.61956574242</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.22531643827</v>
+        <v>4104.225316438271</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.313706498426</v>
@@ -6611,7 +6611,7 @@
         <v>14505.07154964202</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.504455511913</v>
+        <v>7846.504455511915</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.677045112664</v>
@@ -6626,16 +6626,16 @@
         <v>15891.69866157623</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>8428.487521239878</v>
+        <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27001.19068566421</v>
+        <v>27001.19068566422</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17732.25543906577</v>
@@ -6678,7 +6678,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>84.18113861466703</v>
@@ -6693,10 +6693,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -6708,10 +6708,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -6760,7 +6760,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -6815,7 +6815,7 @@
         <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>935.4510916205024</v>
+        <v>935.4510916205021</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>437.9455632273563</v>
@@ -6830,16 +6830,16 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.6985907841487</v>
+        <v>991.6985907841489</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902546</v>
+        <v>458.8712079902547</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.86952507761</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>16092.870139521</v>
+        <v>16092.87013952099</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>4194.47964253869</v>
@@ -7214,31 +7214,31 @@
         <v>5569.086825987128</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814956</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939063</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722068</v>
+        <v>647.3668914722069</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.8295973682</v>
+        <v>8460.829597368196</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.165470626183</v>
+        <v>5846.165470626176</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667305</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.5144261187</v>
+        <v>8909.514426118691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.898890084994</v>
@@ -7247,13 +7247,13 @@
         <v>1766.610866018011</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>654.744813127576</v>
+        <v>654.7448131275778</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>839.5237250909322</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>9403.778294321513</v>
+        <v>9403.778294321515</v>
       </c>
     </row>
     <row r="100">
@@ -8628,7 +8628,7 @@
         <v>36479108.3909279</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>47681.20374516816</v>
+        <v>47681.20374516815</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>98.91374267056001</v>
+        <v>98.91374267056</v>
       </c>
     </row>
     <row r="26">
@@ -8859,7 +8859,7 @@
         <v>10130759.10811187</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>496.3110877494</v>
+        <v>496.3110877493999</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>8104574.014232038</v>
+        <v>8104574.014232036</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>4224.614475448639</v>
+        <v>4224.61447544864</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>7261041.493413354</v>
+        <v>7261041.493413353</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5596493.161870115</v>
+        <v>5596493.161870113</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>795.784626769313</v>
+        <v>795.7846267693131</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9378,7 +9378,7 @@
         <v>3129242.204697554</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>360.8044705626896</v>
+        <v>360.8044705626895</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -9532,7 +9532,7 @@
         <v>2065048.249427686</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>386.735912532</v>
+        <v>386.7359125319999</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9672,7 +9672,7 @@
         <v>1751703.99415768</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>2220.603683210644</v>
+        <v>2220.603683210645</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -9739,7 +9739,7 @@
         <v>1696818.117976401</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>3262.52226153056</v>
+        <v>3262.522261530561</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="AN42" s="58" t="n">
-        <v>337.2342832499999</v>
+        <v>337.23428325</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" thickBot="1">
@@ -10429,13 +10429,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18456847241</v>
+        <v>6320.184568472409</v>
       </c>
       <c r="K53" s="128" t="n">
         <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7692560352087</v>
+        <v>790.7692560352083</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10447,10 +10447,10 @@
         <v>6124.982752775582</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254566</v>
+        <v>3021.852223254567</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8856898136659</v>
+        <v>757.8856898136662</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -10459,19 +10459,19 @@
         <v>9904.720665843814</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.678172337912</v>
+        <v>5957.678172337913</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.103304474578</v>
+        <v>2933.103304474579</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.1979185924263</v>
+        <v>729.1979185924259</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.979395404916</v>
+        <v>9619.979395404918</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
         <v>14502.01308940453</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860365</v>
+        <v>7845.496351860367</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.677045112664</v>
@@ -10522,22 +10522,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>24673.18648637756</v>
+        <v>24673.18648637757</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>15888.66465948535</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>8427.48817443864</v>
+        <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.15733677209</v>
+        <v>26997.1573367721</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.25159470503</v>
@@ -10594,7 +10594,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>84.18113861466703</v>
@@ -10609,10 +10609,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -10624,10 +10624,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -10753,19 +10753,19 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.402957708949</v>
+        <v>6294.40295770895</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>437.3875171463492</v>
+        <v>437.387517146349</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262969340319</v>
+        <v>8174.262969340318</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.281402399409</v>
@@ -10774,7 +10774,7 @@
         <v>1116.162906236298</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>418.4625294433528</v>
+        <v>418.462529443353</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>258.2282688764468</v>
@@ -10783,19 +10783,19 @@
         <v>8033.135106955507</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6382.359151572182</v>
+        <v>6382.359151572181</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1131.374266204664</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.6902841248111</v>
+        <v>419.6902841248108</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8200.83017629315</v>
+        <v>8200.830176293148</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1650870.480105934</v>
+        <v>1650870.480105933</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>4932.342742430019</v>
@@ -11239,34 +11239,34 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.086825987135</v>
+        <v>5569.086825987128</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939058</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>647.3668914722069</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829597368207</v>
+        <v>8460.829597368198</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5846.165470626176</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486477</v>
+        <v>1696.460671486473</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667296</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>738.1509877393058</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514426118691</v>
+        <v>8909.514426118685</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6142.898890084994</v>
@@ -11662,7 +11662,7 @@
         <v>899.5669733810392</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72510.53378779674</v>
+        <v>72510.53378779672</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>54059.89244389046</v>
@@ -11860,13 +11860,13 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6288.269408740671</v>
+        <v>6288.269408740672</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1107.836161362766</v>
+        <v>1107.836161362765</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1518534315276</v>
+        <v>357.1518534315275</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -11875,13 +11875,13 @@
         <v>7753.257423534964</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6400.337036322164</v>
+        <v>6400.337036322165</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9303875207317</v>
+        <v>365.9303875207316</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
@@ -11890,7 +11890,7 @@
         <v>7907.087201444931</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.941393404507</v>
+        <v>6479.941393404506</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.179193274199</v>
+        <v>8024.179193274198</v>
       </c>
     </row>
     <row r="72">
@@ -11945,7 +11945,7 @@
         <v>3.034002090881227</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.9993468012388085</v>
+        <v>0.9993468012388083</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -11954,13 +11954,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.033348892120036</v>
+        <v>4.033348892120035</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.003844360738305</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -11969,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="132" t="n">
-        <v>3.992985467227335</v>
+        <v>3.992985467227334</v>
       </c>
     </row>
     <row r="73">
@@ -12079,7 +12079,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
         <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0635744741532</v>
+        <v>498.0635744741531</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -12152,19 +12152,19 @@
         <v>573.2360613407959</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138078</v>
+        <v>200.6429391138079</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73441812211</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.510987948814</v>
+        <v>9710.510987948812</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>633.2429903122046</v>
+        <v>633.2429903122047</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>215.8071055370164</v>
@@ -12533,46 +12533,46 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="L81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="132" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="P81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="131" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="R81" s="131" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="S81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="132" t="n">
+        <v>5.684341886080801e-13</v>
+      </c>
+      <c r="V81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="131" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="M81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="132" t="n">
-        <v>-2.501110429875553e-12</v>
-      </c>
-      <c r="P81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="Q81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="132" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="V81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="W81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
-      </c>
       <c r="Y81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>-3.751665644813329e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="82">
@@ -12881,7 +12881,7 @@
         <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>19086.22657346602</v>
+        <v>19086.22657346603</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>15525.14577929941</v>
@@ -12893,7 +12893,7 @@
         <v>939.1664488615277</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869956</v>
+        <v>210.6296420869957</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>20593.2471536308</v>
@@ -12911,7 +12911,7 @@
         <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>21876.19741018457</v>
+        <v>21876.19741018458</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13098,7 +13098,7 @@
         <v>12437.61956574242</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.22531643827</v>
+        <v>4104.225316438271</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.313706498426</v>
@@ -13135,7 +13135,7 @@
         <v>14505.07154964202</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.504455511913</v>
+        <v>7846.504455511915</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.677045112664</v>
@@ -13150,16 +13150,16 @@
         <v>15891.69866157623</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>8428.487521239878</v>
+        <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27001.19068566421</v>
+        <v>27001.19068566422</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17732.25543906577</v>
@@ -13202,7 +13202,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>84.18113861466703</v>
@@ -13217,10 +13217,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -13232,10 +13232,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -13284,7 +13284,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -13339,7 +13339,7 @@
         <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>935.4510916205024</v>
+        <v>935.4510916205021</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>437.9455632273563</v>
@@ -13354,16 +13354,16 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.6985907841487</v>
+        <v>991.6985907841489</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902546</v>
+        <v>458.8712079902547</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.86952507761</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>16092.870139521</v>
+        <v>16092.87013952099</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>4194.47964253869</v>
@@ -13738,31 +13738,31 @@
         <v>5569.086825987128</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814956</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939063</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722068</v>
+        <v>647.3668914722069</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.8295973682</v>
+        <v>8460.829597368196</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.165470626183</v>
+        <v>5846.165470626176</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667305</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.5144261187</v>
+        <v>8909.514426118691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.898890084994</v>
@@ -13771,13 +13771,13 @@
         <v>1766.610866018011</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>654.744813127576</v>
+        <v>654.7448131275778</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>839.5237250909322</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>9403.778294321513</v>
+        <v>9403.778294321515</v>
       </c>
     </row>
     <row r="100">
@@ -15152,7 +15152,7 @@
         <v>45235826.03390888</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621584</v>
+        <v>57217.44053621582</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15168,7 +15168,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>98.12243272919551</v>
+        <v>98.12243272919549</v>
       </c>
     </row>
     <row r="26">
@@ -15306,7 +15306,7 @@
         <v>12268638.86353412</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>814.1858468752741</v>
+        <v>814.1858468752743</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3399938.261079619</v>
+        <v>3399938.26107962</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>370.4758201091039</v>
@@ -16133,7 +16133,7 @@
         <v>2204566.834283146</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>397.0037510097246</v>
+        <v>397.0037510097247</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1881452.591852352</v>
+        <v>1881452.591852353</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2122.197973647326</v>
@@ -16263,7 +16263,7 @@
         <v>1861818.454111506</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>3412.859287341887</v>
+        <v>3412.859287341888</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -16340,7 +16340,7 @@
         <v>1749567.748159604</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>4040.673218108398</v>
+        <v>4040.673218108399</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1718570.266011412</v>
+        <v>1718570.266011413</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2581.980991447346</v>
@@ -16953,13 +16953,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18456847241</v>
+        <v>6320.184568472409</v>
       </c>
       <c r="K53" s="128" t="n">
         <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7692560352087</v>
+        <v>790.7692560352083</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16971,10 +16971,10 @@
         <v>6124.982752775582</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254566</v>
+        <v>3021.852223254567</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8856898136659</v>
+        <v>757.8856898136662</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -16983,19 +16983,19 @@
         <v>9904.720665843814</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.678172337912</v>
+        <v>5957.678172337913</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.103304474578</v>
+        <v>2933.103304474579</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.1979185924263</v>
+        <v>729.1979185924259</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.979395404916</v>
+        <v>9619.979395404918</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -17037,7 +17037,7 @@
         <v>14502.01308940453</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860365</v>
+        <v>7845.496351860367</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.677045112664</v>
@@ -17046,22 +17046,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>24673.18648637756</v>
+        <v>24673.18648637757</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>15888.66465948535</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>8427.48817443864</v>
+        <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.15733677209</v>
+        <v>26997.1573367721</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.25159470503</v>
@@ -17118,7 +17118,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>84.18113861466703</v>
@@ -17133,10 +17133,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -17148,10 +17148,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -17171,7 +17171,7 @@
         <v>2908518.618495713</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>426.372871952181</v>
+        <v>426.3728719521811</v>
       </c>
     </row>
     <row r="56">
@@ -17252,7 +17252,7 @@
         <v>2780993.046632514</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>5408.787139759952</v>
+        <v>5408.787139759953</v>
       </c>
     </row>
     <row r="57">
@@ -17277,19 +17277,19 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.402957708949</v>
+        <v>6294.40295770895</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>437.3875171463492</v>
+        <v>437.387517146349</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262969340319</v>
+        <v>8174.262969340318</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.281402399409</v>
@@ -17298,7 +17298,7 @@
         <v>1116.162906236298</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>418.4625294433528</v>
+        <v>418.462529443353</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>258.2282688764468</v>
@@ -17307,19 +17307,19 @@
         <v>8033.135106955507</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6382.359151572182</v>
+        <v>6382.359151572181</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1131.374266204664</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.6902841248111</v>
+        <v>419.6902841248108</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8200.83017629315</v>
+        <v>8200.830176293148</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -17414,7 +17414,7 @@
         <v>1811795.4062178</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>4337.387620661999</v>
+        <v>4337.387620661998</v>
       </c>
     </row>
     <row r="59">
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>884607.9620802102</v>
+        <v>884607.9620802103</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>2371.245811243431</v>
@@ -17763,34 +17763,34 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.086825987135</v>
+        <v>5569.086825987128</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939058</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>647.3668914722069</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829597368207</v>
+        <v>8460.829597368198</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5846.165470626176</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486477</v>
+        <v>1696.460671486473</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667296</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>738.1509877393058</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514426118691</v>
+        <v>8909.514426118685</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6142.898890084994</v>
@@ -18186,7 +18186,7 @@
         <v>899.5669733810392</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72510.53378779674</v>
+        <v>72510.53378779672</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>54059.89244389046</v>
@@ -18384,13 +18384,13 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6288.269408740671</v>
+        <v>6288.269408740672</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1107.836161362766</v>
+        <v>1107.836161362765</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1518534315276</v>
+        <v>357.1518534315275</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -18399,13 +18399,13 @@
         <v>7753.257423534964</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6400.337036322164</v>
+        <v>6400.337036322165</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9303875207317</v>
+        <v>365.9303875207316</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
@@ -18414,7 +18414,7 @@
         <v>7907.087201444931</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.941393404507</v>
+        <v>6479.941393404506</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
@@ -18426,7 +18426,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.179193274199</v>
+        <v>8024.179193274198</v>
       </c>
     </row>
     <row r="72">
@@ -18469,7 +18469,7 @@
         <v>3.034002090881227</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.9993468012388085</v>
+        <v>0.9993468012388083</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -18478,13 +18478,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.033348892120036</v>
+        <v>4.033348892120035</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.003844360738305</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -18493,7 +18493,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="132" t="n">
-        <v>3.992985467227335</v>
+        <v>3.992985467227334</v>
       </c>
     </row>
     <row r="73">
@@ -18603,7 +18603,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -18658,7 +18658,7 @@
         <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0635744741532</v>
+        <v>498.0635744741531</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -18676,19 +18676,19 @@
         <v>573.2360613407959</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138078</v>
+        <v>200.6429391138079</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73441812211</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.510987948814</v>
+        <v>9710.510987948812</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>633.2429903122046</v>
+        <v>633.2429903122047</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>215.8071055370164</v>
@@ -19057,46 +19057,46 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="L81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="132" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="P81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="131" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="R81" s="131" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="S81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="132" t="n">
+        <v>5.684341886080801e-13</v>
+      </c>
+      <c r="V81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="131" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="M81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="132" t="n">
-        <v>-2.501110429875553e-12</v>
-      </c>
-      <c r="P81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="Q81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="132" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="V81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="W81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
-      </c>
       <c r="Y81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>-3.751665644813329e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="82">
@@ -19405,7 +19405,7 @@
         <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>19086.22657346602</v>
+        <v>19086.22657346603</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>15525.14577929941</v>
@@ -19417,7 +19417,7 @@
         <v>939.1664488615277</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869956</v>
+        <v>210.6296420869957</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>20593.2471536308</v>
@@ -19435,7 +19435,7 @@
         <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>21876.19741018457</v>
+        <v>21876.19741018458</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19622,7 +19622,7 @@
         <v>12437.61956574242</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.22531643827</v>
+        <v>4104.225316438271</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.313706498426</v>
@@ -19659,7 +19659,7 @@
         <v>14505.07154964202</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.504455511913</v>
+        <v>7846.504455511915</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.677045112664</v>
@@ -19674,16 +19674,16 @@
         <v>15891.69866157623</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>8428.487521239878</v>
+        <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27001.19068566421</v>
+        <v>27001.19068566422</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17732.25543906577</v>
@@ -19726,7 +19726,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>84.18113861466703</v>
@@ -19741,10 +19741,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -19756,10 +19756,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -19808,7 +19808,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>935.4510916205024</v>
+        <v>935.4510916205021</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>437.9455632273563</v>
@@ -19878,16 +19878,16 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.6985907841487</v>
+        <v>991.6985907841489</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902546</v>
+        <v>458.8712079902547</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.86952507761</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>16092.870139521</v>
+        <v>16092.87013952099</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>4194.47964253869</v>
@@ -20262,31 +20262,31 @@
         <v>5569.086825987128</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814956</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939063</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722068</v>
+        <v>647.3668914722069</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.8295973682</v>
+        <v>8460.829597368196</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.165470626183</v>
+        <v>5846.165470626176</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667305</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.5144261187</v>
+        <v>8909.514426118691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.898890084994</v>
@@ -20295,13 +20295,13 @@
         <v>1766.610866018011</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>654.744813127576</v>
+        <v>654.7448131275778</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>839.5237250909322</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>9403.778294321513</v>
+        <v>9403.778294321515</v>
       </c>
     </row>
     <row r="100">
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55719460.42474839</v>
+        <v>55719460.42474838</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379245</v>
+        <v>68660.92484379248</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>13031677.99235527</v>
+        <v>13031677.99235528</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>6257.992427689867</v>
@@ -22192,10 +22192,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>6528556.355378518</v>
+        <v>6528556.355378519</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>833.552762445304</v>
+        <v>833.5527624453041</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5310405.84253849</v>
+        <v>5310405.842538491</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>17641.43818058407</v>
@@ -22657,7 +22657,7 @@
         <v>2325375.35539304</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>404.9080956923283</v>
+        <v>404.9080956923282</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>69779636.9556046</v>
+        <v>69779636.95560461</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>85020.26381129169</v>
@@ -23331,7 +23331,7 @@
         <v>15006821.13073096</v>
       </c>
       <c r="AH51" s="56" t="n">
-        <v>7001.560687693529</v>
+        <v>7001.56068769353</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" thickBot="1">
@@ -23477,13 +23477,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18456847241</v>
+        <v>6320.184568472409</v>
       </c>
       <c r="K53" s="128" t="n">
         <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7692560352087</v>
+        <v>790.7692560352083</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23495,10 +23495,10 @@
         <v>6124.982752775582</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254566</v>
+        <v>3021.852223254567</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8856898136659</v>
+        <v>757.8856898136662</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -23507,19 +23507,19 @@
         <v>9904.720665843814</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.678172337912</v>
+        <v>5957.678172337913</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.103304474578</v>
+        <v>2933.103304474579</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.1979185924263</v>
+        <v>729.1979185924259</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.979395404916</v>
+        <v>9619.979395404918</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23561,7 +23561,7 @@
         <v>14502.01308940453</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860365</v>
+        <v>7845.496351860367</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.677045112664</v>
@@ -23570,22 +23570,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>24673.18648637756</v>
+        <v>24673.18648637757</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>15888.66465948535</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>8427.48817443864</v>
+        <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.15733677209</v>
+        <v>26997.1573367721</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.25159470503</v>
@@ -23642,7 +23642,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>84.18113861466703</v>
@@ -23657,10 +23657,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -23672,10 +23672,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -23801,19 +23801,19 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.402957708949</v>
+        <v>6294.40295770895</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>437.3875171463492</v>
+        <v>437.387517146349</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262969340319</v>
+        <v>8174.262969340318</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.281402399409</v>
@@ -23822,7 +23822,7 @@
         <v>1116.162906236298</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>418.4625294433528</v>
+        <v>418.462529443353</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>258.2282688764468</v>
@@ -23831,19 +23831,19 @@
         <v>8033.135106955507</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6382.359151572182</v>
+        <v>6382.359151572181</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1131.374266204664</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.6902841248111</v>
+        <v>419.6902841248108</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8200.83017629315</v>
+        <v>8200.830176293148</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1143004.551013211</v>
+        <v>1143004.551013212</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>290.6501226605639</v>
@@ -24287,34 +24287,34 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.086825987135</v>
+        <v>5569.086825987128</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939058</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>647.3668914722069</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829597368207</v>
+        <v>8460.829597368198</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5846.165470626176</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486477</v>
+        <v>1696.460671486473</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667296</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>738.1509877393058</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514426118691</v>
+        <v>8909.514426118685</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6142.898890084994</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>781605.0418458922</v>
+        <v>781605.0418458923</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2350.276413386248</v>
@@ -24710,7 +24710,7 @@
         <v>899.5669733810392</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72510.53378779674</v>
+        <v>72510.53378779672</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>54059.89244389046</v>
@@ -24754,7 +24754,7 @@
         <v>334190.0867178393</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>913.0841014375313</v>
+        <v>913.0841014375312</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -24908,13 +24908,13 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6288.269408740671</v>
+        <v>6288.269408740672</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1107.836161362766</v>
+        <v>1107.836161362765</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1518534315276</v>
+        <v>357.1518534315275</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -24923,13 +24923,13 @@
         <v>7753.257423534964</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6400.337036322164</v>
+        <v>6400.337036322165</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9303875207317</v>
+        <v>365.9303875207316</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
@@ -24938,7 +24938,7 @@
         <v>7907.087201444931</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.941393404507</v>
+        <v>6479.941393404506</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
@@ -24950,7 +24950,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.179193274199</v>
+        <v>8024.179193274198</v>
       </c>
     </row>
     <row r="72">
@@ -24993,7 +24993,7 @@
         <v>3.034002090881227</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.9993468012388085</v>
+        <v>0.9993468012388083</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -25002,13 +25002,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.033348892120036</v>
+        <v>4.033348892120035</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.003844360738305</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -25017,7 +25017,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="132" t="n">
-        <v>3.992985467227335</v>
+        <v>3.992985467227334</v>
       </c>
     </row>
     <row r="73">
@@ -25127,7 +25127,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -25182,7 +25182,7 @@
         <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0635744741532</v>
+        <v>498.0635744741531</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -25200,19 +25200,19 @@
         <v>573.2360613407959</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138078</v>
+        <v>200.6429391138079</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73441812211</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.510987948814</v>
+        <v>9710.510987948812</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>633.2429903122046</v>
+        <v>633.2429903122047</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>215.8071055370164</v>
@@ -25581,46 +25581,46 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="L81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="132" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="P81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="131" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="R81" s="131" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="S81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="132" t="n">
+        <v>5.684341886080801e-13</v>
+      </c>
+      <c r="V81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="131" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="M81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="132" t="n">
-        <v>-2.501110429875553e-12</v>
-      </c>
-      <c r="P81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="Q81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="132" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="V81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="W81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
-      </c>
       <c r="Y81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>-3.751665644813329e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="82">
@@ -25929,7 +25929,7 @@
         <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>19086.22657346602</v>
+        <v>19086.22657346603</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>15525.14577929941</v>
@@ -25941,7 +25941,7 @@
         <v>939.1664488615277</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869956</v>
+        <v>210.6296420869957</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>20593.2471536308</v>
@@ -25959,7 +25959,7 @@
         <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>21876.19741018457</v>
+        <v>21876.19741018458</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26146,7 +26146,7 @@
         <v>12437.61956574242</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.22531643827</v>
+        <v>4104.225316438271</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.313706498426</v>
@@ -26183,7 +26183,7 @@
         <v>14505.07154964202</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.504455511913</v>
+        <v>7846.504455511915</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.677045112664</v>
@@ -26198,16 +26198,16 @@
         <v>15891.69866157623</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>8428.487521239878</v>
+        <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27001.19068566421</v>
+        <v>27001.19068566422</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17732.25543906577</v>
@@ -26250,7 +26250,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>84.18113861466703</v>
@@ -26265,10 +26265,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -26280,10 +26280,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -26332,7 +26332,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>935.4510916205024</v>
+        <v>935.4510916205021</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>437.9455632273563</v>
@@ -26402,16 +26402,16 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.6985907841487</v>
+        <v>991.6985907841489</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902546</v>
+        <v>458.8712079902547</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.86952507761</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>16092.870139521</v>
+        <v>16092.87013952099</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>4194.47964253869</v>
@@ -26786,31 +26786,31 @@
         <v>5569.086825987128</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814956</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939063</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722068</v>
+        <v>647.3668914722069</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.8295973682</v>
+        <v>8460.829597368196</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.165470626183</v>
+        <v>5846.165470626176</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667305</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.5144261187</v>
+        <v>8909.514426118691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.898890084994</v>
@@ -26819,13 +26819,13 @@
         <v>1766.610866018011</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>654.744813127576</v>
+        <v>654.7448131275778</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>839.5237250909322</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>9403.778294321513</v>
+        <v>9403.778294321515</v>
       </c>
     </row>
     <row r="100">
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69285584.18914482</v>
+        <v>69285584.18914483</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28293,7 +28293,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>96.24752498419527</v>
+        <v>96.24752498419528</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -28431,7 +28431,7 @@
         <v>16598675.10338615</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>7591.883513651961</v>
+        <v>7591.88351365196</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>14570481.40100323</v>
+        <v>14570481.40100322</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28585,7 +28585,7 @@
         <v>11270906.34641929</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>529.9779303762052</v>
+        <v>529.9779303762053</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7082919.956535397</v>
+        <v>7082919.956535398</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>850.356497390649</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6109904.890164005</v>
+        <v>6109904.890164007</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>19791.41132971137</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3345148.128947593</v>
+        <v>3345148.128947594</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29181,7 +29181,7 @@
         <v>2605315.839764418</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>5626.233388894135</v>
+        <v>5626.233388894134</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2478636.557893779</v>
+        <v>2478636.55789378</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>412.9698158775626</v>
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>49.9387245724173</v>
+        <v>49.93872457241729</v>
       </c>
     </row>
     <row r="42">
@@ -29542,7 +29542,7 @@
         <v>1628208.049291219</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>2218.827294049513</v>
+        <v>2218.827294049512</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -30001,13 +30001,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.18456847241</v>
+        <v>6320.184568472409</v>
       </c>
       <c r="K53" s="128" t="n">
         <v>3125.418230837481</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7692560352087</v>
+        <v>790.7692560352083</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30019,10 +30019,10 @@
         <v>6124.982752775582</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3021.852223254566</v>
+        <v>3021.852223254567</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.8856898136659</v>
+        <v>757.8856898136662</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
@@ -30031,19 +30031,19 @@
         <v>9904.720665843814</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.678172337912</v>
+        <v>5957.678172337913</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>2933.103304474578</v>
+        <v>2933.103304474579</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.1979185924263</v>
+        <v>729.1979185924259</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>9619.979395404916</v>
+        <v>9619.979395404918</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6596561.730730158</v>
+        <v>6596561.730730157</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>21621.77584583756</v>
@@ -30085,7 +30085,7 @@
         <v>14502.01308940453</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.496351860365</v>
+        <v>7845.496351860367</v>
       </c>
       <c r="L54" s="131" t="n">
         <v>2325.677045112664</v>
@@ -30094,22 +30094,22 @@
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>24673.18648637756</v>
+        <v>24673.18648637757</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>15888.66465948535</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>8427.48817443864</v>
+        <v>8427.488174438642</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="132" t="n">
-        <v>26997.15733677209</v>
+        <v>26997.1573367721</v>
       </c>
       <c r="V54" s="130" t="n">
         <v>17729.25159470503</v>
@@ -30166,7 +30166,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>84.18113861466703</v>
@@ -30181,10 +30181,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -30196,10 +30196,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W55" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -30325,19 +30325,19 @@
         <v>15717</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6294.402957708949</v>
+        <v>6294.40295770895</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1190.272412576187</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>437.3875171463492</v>
+        <v>437.387517146349</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>252.2000819088323</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8174.262969340319</v>
+        <v>8174.262969340318</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6240.281402399409</v>
@@ -30346,7 +30346,7 @@
         <v>1116.162906236298</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>418.4625294433528</v>
+        <v>418.462529443353</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>258.2282688764468</v>
@@ -30355,19 +30355,19 @@
         <v>8033.135106955507</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6382.359151572182</v>
+        <v>6382.359151572181</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1131.374266204664</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>419.6902841248111</v>
+        <v>419.6902841248108</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>267.4064743914916</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>8200.83017629315</v>
+        <v>8200.830176293148</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -30811,34 +30811,34 @@
         <v>5122</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5569.086825987135</v>
+        <v>5569.086825987128</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814957</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939058</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>647.3668914722069</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>8460.829597368207</v>
+        <v>8460.829597368198</v>
       </c>
       <c r="P63" s="130" t="n">
         <v>5846.165470626176</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1696.460671486477</v>
+        <v>1696.460671486473</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667296</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>738.1509877393058</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8909.514426118691</v>
+        <v>8909.514426118685</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6142.898890084994</v>
@@ -31197,7 +31197,7 @@
         <v>347285.1570508346</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>905.9255220822612</v>
+        <v>905.9255220822611</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -31234,7 +31234,7 @@
         <v>899.5669733810392</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72510.53378779674</v>
+        <v>72510.53378779672</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>54059.89244389046</v>
@@ -31432,13 +31432,13 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6288.269408740671</v>
+        <v>6288.269408740672</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1107.836161362766</v>
+        <v>1107.836161362765</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.1518534315276</v>
+        <v>357.1518534315275</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
@@ -31447,13 +31447,13 @@
         <v>7753.257423534964</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6400.337036322164</v>
+        <v>6400.337036322165</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.819777602035</v>
       </c>
       <c r="R71" s="128" t="n">
-        <v>365.9303875207317</v>
+        <v>365.9303875207316</v>
       </c>
       <c r="S71" s="128" t="n">
         <v>0</v>
@@ -31462,7 +31462,7 @@
         <v>7907.087201444931</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6479.941393404507</v>
+        <v>6479.941393404506</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.122011963692</v>
@@ -31474,7 +31474,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8024.179193274199</v>
+        <v>8024.179193274198</v>
       </c>
     </row>
     <row r="72">
@@ -31517,7 +31517,7 @@
         <v>3.034002090881227</v>
       </c>
       <c r="Q72" s="131" t="n">
-        <v>0.9993468012388085</v>
+        <v>0.9993468012388083</v>
       </c>
       <c r="R72" s="131" t="n">
         <v>0</v>
@@ -31526,13 +31526,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.033348892120036</v>
+        <v>4.033348892120035</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.003844360738305</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891411064890299</v>
+        <v>0.9891411064890296</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -31541,7 +31541,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="132" t="n">
-        <v>3.992985467227335</v>
+        <v>3.992985467227334</v>
       </c>
     </row>
     <row r="73">
@@ -31651,7 +31651,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q74" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R74" s="131" t="n">
         <v>0</v>
@@ -31706,7 +31706,7 @@
         <v>2391.347471371049</v>
       </c>
       <c r="L75" s="131" t="n">
-        <v>498.0635744741532</v>
+        <v>498.0635744741531</v>
       </c>
       <c r="M75" s="131" t="n">
         <v>185.745481318524</v>
@@ -31724,19 +31724,19 @@
         <v>573.2360613407959</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>200.6429391138078</v>
+        <v>200.6429391138079</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12463.73441812211</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>9710.510987948814</v>
+        <v>9710.510987948812</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3063.105376334026</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>633.2429903122046</v>
+        <v>633.2429903122047</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>215.8071055370164</v>
@@ -32105,46 +32105,46 @@
         <v>-1.818989403545856e-12</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="L81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="132" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="P81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="131" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="R81" s="131" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="S81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="132" t="n">
+        <v>5.684341886080801e-13</v>
+      </c>
+      <c r="V81" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" s="131" t="n">
         <v>-2.273736754432321e-13</v>
       </c>
-      <c r="M81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="132" t="n">
-        <v>-2.501110429875553e-12</v>
-      </c>
-      <c r="P81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="Q81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" s="132" t="n">
-        <v>1.818989403545856e-12</v>
-      </c>
-      <c r="V81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="W81" s="131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="131" t="n">
-        <v>-1.13686837721616e-13</v>
-      </c>
       <c r="Y81" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>-3.751665644813329e-12</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="82">
@@ -32453,7 +32453,7 @@
         <v>196.3800389497603</v>
       </c>
       <c r="N86" s="144" t="n">
-        <v>19086.22657346602</v>
+        <v>19086.22657346603</v>
       </c>
       <c r="P86" s="142" t="n">
         <v>15525.14577929941</v>
@@ -32465,7 +32465,7 @@
         <v>939.1664488615277</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>210.6296420869956</v>
+        <v>210.6296420869957</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>20593.2471536308</v>
@@ -32483,7 +32483,7 @@
         <v>225.2747284036044</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>21876.19741018457</v>
+        <v>21876.19741018458</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32670,7 +32670,7 @@
         <v>12437.61956574242</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4104.22531643827</v>
+        <v>4104.225316438271</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1102.313706498426</v>
@@ -32707,7 +32707,7 @@
         <v>14505.07154964202</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.504455511913</v>
+        <v>7846.504455511915</v>
       </c>
       <c r="L90" s="131" t="n">
         <v>2325.677045112664</v>
@@ -32722,16 +32722,16 @@
         <v>15891.69866157623</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>8428.487521239878</v>
+        <v>8428.48752123988</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>2681.0045028481</v>
+        <v>2681.004502848102</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27001.19068566421</v>
+        <v>27001.19068566422</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17732.25543906577</v>
@@ -32774,7 +32774,7 @@
         <v>19989.70418712685</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>891.9973536240338</v>
+        <v>891.997353624034</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>84.18113861466703</v>
@@ -32789,10 +32789,10 @@
         <v>19959.79815860394</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.6435942987473</v>
+        <v>890.6435942987475</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>84.04593133098501</v>
+        <v>84.04593133098508</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -32804,10 +32804,10 @@
         <v>19890.30405004525</v>
       </c>
       <c r="W91" s="131" t="n">
-        <v>887.5253429324022</v>
+        <v>887.5253429324024</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>83.74123998569763</v>
+        <v>83.74123998569762</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -32856,7 +32856,7 @@
         <v>184.6096104752861</v>
       </c>
       <c r="Q92" s="131" t="n">
-        <v>23.79587172316868</v>
+        <v>23.79587172316867</v>
       </c>
       <c r="R92" s="131" t="n">
         <v>0</v>
@@ -32911,7 +32911,7 @@
         <v>3581.619883947236</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>935.4510916205024</v>
+        <v>935.4510916205021</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>437.9455632273563</v>
@@ -32926,16 +32926,16 @@
         <v>3868.853193492727</v>
       </c>
       <c r="R93" s="131" t="n">
-        <v>991.6985907841487</v>
+        <v>991.6985907841489</v>
       </c>
       <c r="S93" s="131" t="n">
-        <v>458.8712079902546</v>
+        <v>458.8712079902547</v>
       </c>
       <c r="T93" s="132" t="n">
         <v>20496.86952507761</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>16092.870139521</v>
+        <v>16092.87013952099</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>4194.47964253869</v>
@@ -33310,31 +33310,31 @@
         <v>5569.086825987128</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1638.834737814959</v>
+        <v>1638.834737814956</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>605.5411420939054</v>
+        <v>605.5411420939063</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>647.3668914722068</v>
+        <v>647.3668914722069</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>8460.8295973682</v>
+        <v>8460.829597368196</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>5846.165470626183</v>
+        <v>5846.165470626176</v>
       </c>
       <c r="Q99" s="131" t="n">
         <v>1696.460671486479</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>628.7372962667323</v>
+        <v>628.7372962667305</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>738.1509877393057</v>
+        <v>738.1509877393059</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>8909.5144261187</v>
+        <v>8909.514426118691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>6142.898890084994</v>
@@ -33343,13 +33343,13 @@
         <v>1766.610866018011</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>654.744813127576</v>
+        <v>654.7448131275778</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>839.5237250909322</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>9403.778294321513</v>
+        <v>9403.778294321515</v>
       </c>
     </row>
     <row r="100">
